--- a/grupos/5BLCM - Estadisticos 20241.xlsx
+++ b/grupos/5BLCM - Estadisticos 20241.xlsx
@@ -777,22 +777,22 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -819,13 +819,13 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -854,22 +854,22 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -931,22 +931,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -973,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1008,22 +1008,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1085,22 +1085,22 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1124,10 +1124,10 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1162,22 +1162,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1204,7 +1204,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1239,22 +1239,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1278,16 +1278,16 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1316,22 +1316,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1355,7 +1355,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1393,22 +1393,22 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1432,16 +1432,16 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>6</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1470,22 +1470,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1509,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1518,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1547,22 +1547,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1589,7 +1589,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1624,22 +1624,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1701,22 +1701,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1743,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1778,22 +1778,22 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1814,22 +1814,22 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>5</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1855,22 +1855,22 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1897,13 +1897,13 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -1932,22 +1932,22 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2009,22 +2009,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2057,7 +2057,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2086,22 +2086,22 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2163,22 +2163,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2202,7 +2202,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2240,22 +2240,22 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2279,7 +2279,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2317,22 +2317,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2353,22 +2353,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2394,22 +2394,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2433,10 +2433,10 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2471,22 +2471,22 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2548,22 +2548,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2590,7 +2590,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2625,22 +2625,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2664,10 +2664,10 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2702,22 +2702,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2738,13 +2738,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -2753,7 +2753,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2779,22 +2779,22 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2818,7 +2818,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -2827,7 +2827,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2856,22 +2856,22 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2895,10 +2895,10 @@
         <v>10</v>
       </c>
       <c r="U31">
+        <v>9</v>
+      </c>
+      <c r="V31">
         <v>8</v>
-      </c>
-      <c r="V31">
-        <v>7</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -2933,22 +2933,22 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2972,7 +2972,7 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>8</v>
@@ -2981,7 +2981,7 @@
         <v>7</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3010,22 +3010,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3049,16 +3049,16 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>5</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3087,22 +3087,22 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3126,16 +3126,16 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>6</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3164,22 +3164,22 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3203,7 +3203,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3241,22 +3241,22 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3280,7 +3280,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3318,22 +3318,22 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3357,7 +3357,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>10</v>
@@ -3395,22 +3395,22 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3437,7 +3437,7 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3472,22 +3472,22 @@
         <v>9</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3508,10 +3508,10 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>9</v>
@@ -3520,10 +3520,10 @@
         <v>5</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3659,40 +3659,40 @@
         <v>83.3</v>
       </c>
       <c r="H4">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I4">
         <v>100</v>
       </c>
       <c r="J4">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K4">
         <v>82.59999999999999</v>
       </c>
       <c r="L4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M4">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="N4">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q4">
         <v>82.59999999999999</v>
       </c>
       <c r="R4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S4">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3724,13 +3724,13 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -3742,13 +3742,13 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3783,7 +3783,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3801,7 +3801,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3842,13 +3842,13 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3860,13 +3860,13 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3901,13 +3901,13 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -3919,13 +3919,13 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3960,13 +3960,13 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3978,13 +3978,13 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4019,7 +4019,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -4037,7 +4037,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -4096,7 +4096,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4131,40 +4131,40 @@
         <v>90</v>
       </c>
       <c r="H12">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I12">
         <v>100</v>
       </c>
       <c r="J12">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M12">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N12">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S12">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4196,7 +4196,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4214,7 +4214,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4255,13 +4255,13 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -4273,13 +4273,13 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4314,7 +4314,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4332,7 +4332,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4373,13 +4373,13 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -4391,13 +4391,13 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4426,13 +4426,13 @@
         <v>93.3</v>
       </c>
       <c r="H17">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K17">
         <v>82.59999999999999</v>
@@ -4441,16 +4441,16 @@
         <v>96</v>
       </c>
       <c r="M17">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="N17">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q17">
         <v>82.59999999999999</v>
@@ -4459,7 +4459,7 @@
         <v>96</v>
       </c>
       <c r="S17">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4491,13 +4491,13 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -4509,13 +4509,13 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4550,7 +4550,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4568,7 +4568,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4609,7 +4609,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -4627,7 +4627,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4668,7 +4668,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -4686,7 +4686,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4727,13 +4727,13 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -4745,13 +4745,13 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4780,40 +4780,40 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4839,40 +4839,40 @@
         <v>93.3</v>
       </c>
       <c r="H24">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="I24">
         <v>100</v>
       </c>
       <c r="J24">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="K24">
         <v>91.3</v>
       </c>
       <c r="L24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M24">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="N24">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="Q24">
         <v>91.3</v>
       </c>
       <c r="R24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S24">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4904,13 +4904,13 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K25">
         <v>91.3</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -4922,13 +4922,13 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q25">
         <v>91.3</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4963,13 +4963,13 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -4981,13 +4981,13 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5016,40 +5016,40 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I27">
         <v>100</v>
       </c>
       <c r="J27">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5081,13 +5081,13 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>69</v>
+        <v>83.3</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -5099,13 +5099,13 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>69</v>
+        <v>83.3</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5134,40 +5134,40 @@
         <v>93.3</v>
       </c>
       <c r="H29">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="I29">
         <v>100</v>
       </c>
       <c r="J29">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M29">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="N29">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S29">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5193,40 +5193,40 @@
         <v>93.3</v>
       </c>
       <c r="H30">
-        <v>90</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I30">
         <v>100</v>
       </c>
       <c r="J30">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M30">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N30">
-        <v>90</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>82.8</v>
+        <v>90.7</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S30">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5258,7 +5258,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K31">
         <v>87</v>
@@ -5276,7 +5276,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q31">
         <v>87</v>
@@ -5311,13 +5311,13 @@
         <v>93.3</v>
       </c>
       <c r="H32">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="I32">
         <v>100</v>
       </c>
       <c r="J32">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5326,16 +5326,16 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N32">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>86.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5344,7 +5344,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5376,7 +5376,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K33">
         <v>82.59999999999999</v>
@@ -5394,7 +5394,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q33">
         <v>82.59999999999999</v>
@@ -5429,7 +5429,7 @@
         <v>96.7</v>
       </c>
       <c r="H34">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I34">
         <v>100</v>
@@ -5441,13 +5441,13 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M34">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5459,10 +5459,10 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S34">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5494,7 +5494,7 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>69</v>
+        <v>83.3</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -5512,7 +5512,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>69</v>
+        <v>83.3</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -5553,13 +5553,13 @@
         <v>100</v>
       </c>
       <c r="J36">
-        <v>69</v>
+        <v>83.3</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -5571,13 +5571,13 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>69</v>
+        <v>83.3</v>
       </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -5612,7 +5612,7 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>69</v>
+        <v>83.3</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -5621,7 +5621,7 @@
         <v>100</v>
       </c>
       <c r="M37">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N37">
         <v>100</v>
@@ -5630,7 +5630,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>69</v>
+        <v>83.3</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -5639,7 +5639,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5665,40 +5665,40 @@
         <v>96.7</v>
       </c>
       <c r="H38">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="I38">
         <v>100</v>
       </c>
       <c r="J38">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K38">
         <v>82.59999999999999</v>
       </c>
       <c r="L38">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M38">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="N38">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="O38">
         <v>100</v>
       </c>
       <c r="P38">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q38">
         <v>82.59999999999999</v>
       </c>
       <c r="R38">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S38">
-        <v>96.7</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5724,40 +5724,40 @@
         <v>93.3</v>
       </c>
       <c r="H39">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="I39">
         <v>100</v>
       </c>
       <c r="J39">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K39">
         <v>82.59999999999999</v>
       </c>
       <c r="L39">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M39">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="N39">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="O39">
         <v>100</v>
       </c>
       <c r="P39">
-        <v>79.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q39">
         <v>82.59999999999999</v>
       </c>
       <c r="R39">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S39">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
     </row>
   </sheetData>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5931,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5BLCM - Estadisticos 20241.xlsx
+++ b/grupos/5BLCM - Estadisticos 20241.xlsx
@@ -200,7 +200,7 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
+    <t>Martínez Sota Luis Rey</t>
   </si>
   <si>
     <t>Ramírez Vargas Miranda Alejandra</t>

--- a/grupos/5BLCM - Estadisticos 20241.xlsx
+++ b/grupos/5BLCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="69">
   <si>
     <t>Materia</t>
   </si>
@@ -200,18 +200,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Hernandez Alonso Antonio Ascari</t>
+  </si>
+  <si>
     <t>Martínez Sota Luis Rey</t>
   </si>
   <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -225,51 +225,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
   </si>
 </sst>
 </file>
@@ -786,7 +741,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -822,7 +777,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -863,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -899,7 +854,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -940,7 +895,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -976,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1017,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1053,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1094,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1130,7 +1085,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1171,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1248,7 +1203,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1284,7 +1239,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1325,7 +1280,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1361,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1402,7 +1357,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1438,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1479,7 +1434,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1515,7 +1470,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1556,7 +1511,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1592,7 +1547,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1633,7 +1588,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1710,7 +1665,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1746,7 +1701,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1787,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -1823,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -1864,7 +1819,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -1900,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1941,7 +1896,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2018,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2054,7 +2009,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2095,7 +2050,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2131,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2172,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2249,7 +2204,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2285,7 +2240,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2326,7 +2281,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2362,7 +2317,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2403,7 +2358,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2439,7 +2394,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2480,7 +2435,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2557,7 +2512,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2593,7 +2548,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2634,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2670,7 +2625,7 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2711,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -2747,7 +2702,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2788,7 +2743,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -2824,7 +2779,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -2865,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -2942,7 +2897,7 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -2978,7 +2933,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3019,7 +2974,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3055,7 +3010,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3096,7 +3051,7 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3132,7 +3087,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3173,7 +3128,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -3209,7 +3164,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3250,7 +3205,7 @@
         <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3286,7 +3241,7 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3327,7 +3282,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -3404,7 +3359,7 @@
         <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>8</v>
@@ -3440,7 +3395,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -3481,7 +3436,7 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -3517,7 +3472,7 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -3668,7 +3623,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="K4">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="L4">
         <v>90</v>
@@ -3686,7 +3641,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="R4">
         <v>90</v>
@@ -4081,7 +4036,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4099,7 +4054,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4435,7 +4390,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K17">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="L17">
         <v>96</v>
@@ -4453,7 +4408,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q17">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="R17">
         <v>96</v>
@@ -4848,7 +4803,7 @@
         <v>90.7</v>
       </c>
       <c r="K24">
-        <v>91.3</v>
+        <v>95.3</v>
       </c>
       <c r="L24">
         <v>98</v>
@@ -4866,7 +4821,7 @@
         <v>90.7</v>
       </c>
       <c r="Q24">
-        <v>91.3</v>
+        <v>95.3</v>
       </c>
       <c r="R24">
         <v>98</v>
@@ -4907,7 +4862,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="K25">
-        <v>91.3</v>
+        <v>95.3</v>
       </c>
       <c r="L25">
         <v>98</v>
@@ -4925,7 +4880,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="Q25">
-        <v>91.3</v>
+        <v>95.3</v>
       </c>
       <c r="R25">
         <v>98</v>
@@ -5261,7 +5216,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="K31">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L31">
         <v>92</v>
@@ -5279,7 +5234,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="Q31">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="R31">
         <v>92</v>
@@ -5379,7 +5334,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K33">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="L33">
         <v>96</v>
@@ -5397,7 +5352,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q33">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="R33">
         <v>96</v>
@@ -5674,7 +5629,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K38">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="L38">
         <v>90</v>
@@ -5692,7 +5647,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q38">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="R38">
         <v>90</v>
@@ -5733,7 +5688,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K39">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="L39">
         <v>98</v>
@@ -5751,7 +5706,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q39">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="R39">
         <v>98</v>
@@ -5814,7 +5769,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -5823,19 +5778,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>86.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5846,7 +5801,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -5867,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5878,7 +5833,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -5899,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5910,7 +5865,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -5931,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6045,7 +6000,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6075,121 +6030,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920246</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920110</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920144</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920176</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920148</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5BLCM - Estadisticos 20241.xlsx
+++ b/grupos/5BLCM - Estadisticos 20241.xlsx
@@ -750,10 +750,10 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -762,10 +762,10 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -780,7 +780,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -827,10 +827,10 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -839,10 +839,10 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -904,10 +904,10 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -916,10 +916,10 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -981,10 +981,10 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -993,10 +993,10 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1058,10 +1058,10 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1070,10 +1070,10 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1135,10 +1135,10 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1147,10 +1147,10 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1212,10 +1212,10 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1224,10 +1224,10 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1289,10 +1289,10 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1301,10 +1301,10 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1316,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1366,10 +1366,10 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1378,16 +1378,16 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1443,10 +1443,10 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1455,10 +1455,10 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1520,10 +1520,10 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1532,10 +1532,10 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1597,10 +1597,10 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1609,10 +1609,10 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1674,10 +1674,10 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1686,10 +1686,10 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1751,10 +1751,10 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1763,10 +1763,10 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1828,10 +1828,10 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1840,13 +1840,13 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -1861,7 +1861,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1905,10 +1905,10 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -1917,10 +1917,10 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -1982,10 +1982,10 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -1994,10 +1994,10 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2050,7 +2050,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2059,10 +2059,10 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2071,10 +2071,10 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2086,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2136,10 +2136,10 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2148,10 +2148,10 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2213,10 +2213,10 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2225,10 +2225,10 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2290,10 +2290,10 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2302,10 +2302,10 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2367,10 +2367,10 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2379,10 +2379,10 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2444,10 +2444,10 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2456,10 +2456,10 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2521,10 +2521,10 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2533,10 +2533,10 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2598,10 +2598,10 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2610,10 +2610,10 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2628,7 +2628,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2675,10 +2675,10 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2687,10 +2687,10 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2752,10 +2752,10 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2764,10 +2764,10 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2782,7 +2782,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2829,10 +2829,10 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -2841,10 +2841,10 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2906,10 +2906,10 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -2918,10 +2918,10 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -2936,7 +2936,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -2983,10 +2983,10 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -2995,10 +2995,10 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3060,10 +3060,10 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3072,16 +3072,16 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>10</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3090,7 +3090,7 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3137,10 +3137,10 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3149,10 +3149,10 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3214,10 +3214,10 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3226,16 +3226,16 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3291,10 +3291,10 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3303,10 +3303,10 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3368,10 +3368,10 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3380,10 +3380,10 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3398,7 +3398,7 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>9</v>
@@ -3445,10 +3445,10 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3457,10 +3457,10 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3632,7 +3632,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="N4">
-        <v>87.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3644,10 +3644,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="R4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="S4">
-        <v>87.90000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3703,10 +3703,10 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3750,7 +3750,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3762,10 +3762,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3809,7 +3809,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3821,10 +3821,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3880,7 +3880,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3939,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4045,7 +4045,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -4060,7 +4060,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4104,7 +4104,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N12">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4116,10 +4116,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>94</v>
+        <v>92.5</v>
       </c>
       <c r="S12">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4175,7 +4175,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4234,7 +4234,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4293,7 +4293,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4352,7 +4352,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4399,7 +4399,7 @@
         <v>97</v>
       </c>
       <c r="N17">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4411,10 +4411,10 @@
         <v>90.7</v>
       </c>
       <c r="R17">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S17">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4458,7 +4458,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -4470,10 +4470,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4588,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -4706,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4753,7 +4753,7 @@
         <v>97</v>
       </c>
       <c r="N23">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -4765,10 +4765,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>96</v>
+        <v>93.8</v>
       </c>
       <c r="S23">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4812,7 +4812,7 @@
         <v>97</v>
       </c>
       <c r="N24">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4824,10 +4824,10 @@
         <v>95.3</v>
       </c>
       <c r="R24">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="S24">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4883,7 +4883,7 @@
         <v>95.3</v>
       </c>
       <c r="R25">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4942,7 +4942,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4989,7 +4989,7 @@
         <v>97</v>
       </c>
       <c r="N27">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -5001,10 +5001,10 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="S27">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5060,10 +5060,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5107,7 +5107,7 @@
         <v>97</v>
       </c>
       <c r="N29">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -5119,10 +5119,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S29">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5166,7 +5166,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="N30">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -5178,10 +5178,10 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="S30">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5225,7 +5225,7 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5237,10 +5237,10 @@
         <v>93</v>
       </c>
       <c r="R31">
-        <v>92</v>
+        <v>88.8</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5284,7 +5284,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N32">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -5296,10 +5296,10 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S32">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5355,7 +5355,7 @@
         <v>90.7</v>
       </c>
       <c r="R33">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5402,7 +5402,7 @@
         <v>95.5</v>
       </c>
       <c r="N34">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5414,10 +5414,10 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>94</v>
+        <v>92.5</v>
       </c>
       <c r="S34">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5532,7 +5532,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -5591,10 +5591,10 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S37">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5638,7 +5638,7 @@
         <v>97</v>
       </c>
       <c r="N38">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
       <c r="O38">
         <v>100</v>
@@ -5650,10 +5650,10 @@
         <v>90.7</v>
       </c>
       <c r="R38">
-        <v>90</v>
+        <v>86.3</v>
       </c>
       <c r="S38">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5697,7 +5697,7 @@
         <v>95.5</v>
       </c>
       <c r="N39">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O39">
         <v>100</v>
@@ -5709,10 +5709,10 @@
         <v>90.7</v>
       </c>
       <c r="R39">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="S39">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
   </sheetData>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5886,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/5BLCM - Estadisticos 20241.xlsx
+++ b/grupos/5BLCM - Estadisticos 20241.xlsx
@@ -756,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -833,7 +833,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -910,7 +910,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -987,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1064,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1141,7 +1141,7 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1295,7 +1295,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1449,7 +1449,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1467,7 +1467,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1526,7 +1526,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1603,7 +1603,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1680,7 +1680,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1834,7 +1834,7 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -1911,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -1988,7 +1988,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2065,7 +2065,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2142,7 +2142,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2219,7 +2219,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2373,7 +2373,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2450,7 +2450,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2527,7 +2527,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2545,7 +2545,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2604,7 +2604,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2681,7 +2681,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2758,7 +2758,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2835,7 +2835,7 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -2912,7 +2912,7 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -2989,7 +2989,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3007,7 +3007,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3066,7 +3066,7 @@
         <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3143,7 +3143,7 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3161,7 +3161,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3220,7 +3220,7 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3297,7 +3297,7 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3374,7 +3374,7 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3392,7 +3392,7 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -3451,7 +3451,7 @@
         <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3638,7 +3638,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q4">
         <v>88.40000000000001</v>
@@ -3697,7 +3697,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>90.7</v>
+        <v>94</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3756,7 +3756,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>88.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3815,7 +3815,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3874,7 +3874,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>88.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3933,7 +3933,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3992,7 +3992,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4051,7 +4051,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q11">
         <v>97.7</v>
@@ -4110,7 +4110,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>90.7</v>
+        <v>94</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4169,7 +4169,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4228,7 +4228,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4287,7 +4287,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4346,7 +4346,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4405,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>88.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q17">
         <v>90.7</v>
@@ -4464,7 +4464,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4523,7 +4523,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4582,7 +4582,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4641,7 +4641,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4700,7 +4700,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4759,7 +4759,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4818,7 +4818,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>90.7</v>
+        <v>94</v>
       </c>
       <c r="Q24">
         <v>95.3</v>
@@ -4877,7 +4877,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q25">
         <v>95.3</v>
@@ -4936,7 +4936,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4995,7 +4995,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>90.7</v>
+        <v>94</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5054,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>83.3</v>
+        <v>89.3</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5113,7 +5113,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>88.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5172,7 +5172,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>90.7</v>
+        <v>94</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5231,7 +5231,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q31">
         <v>93</v>
@@ -5290,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5349,7 +5349,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>88.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q33">
         <v>90.7</v>
@@ -5467,7 +5467,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>83.3</v>
+        <v>89.3</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -5526,7 +5526,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>83.3</v>
+        <v>89.3</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -5585,7 +5585,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>83.3</v>
+        <v>89.3</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -5644,7 +5644,7 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>88.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q38">
         <v>90.7</v>
@@ -5703,7 +5703,7 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>88.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q39">
         <v>90.7</v>

--- a/grupos/5BLCM - Estadisticos 20241.xlsx
+++ b/grupos/5BLCM - Estadisticos 20241.xlsx
@@ -759,7 +759,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -836,7 +836,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -913,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -990,7 +990,7 @@
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1067,7 +1067,7 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1144,7 +1144,7 @@
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1221,7 +1221,7 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1298,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1452,7 +1452,7 @@
         <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -1470,7 +1470,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1529,7 +1529,7 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -1606,7 +1606,7 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -1683,7 +1683,7 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -1760,7 +1760,7 @@
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -1837,7 +1837,7 @@
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -1914,7 +1914,7 @@
         <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -1932,7 +1932,7 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -1991,7 +1991,7 @@
         <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -2068,7 +2068,7 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>10</v>
@@ -2145,7 +2145,7 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>10</v>
@@ -2222,7 +2222,7 @@
         <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -2299,7 +2299,7 @@
         <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2453,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2548,7 +2548,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2607,7 +2607,7 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>8</v>
@@ -2684,7 +2684,7 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -2761,7 +2761,7 @@
         <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>9</v>
@@ -2779,7 +2779,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -2838,7 +2838,7 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
         <v>8</v>
@@ -2915,7 +2915,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>7</v>
@@ -2992,7 +2992,7 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -3069,7 +3069,7 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
         <v>7</v>
@@ -3146,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -3223,7 +3223,7 @@
         <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>10</v>
@@ -3300,7 +3300,7 @@
         <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>10</v>
@@ -3377,7 +3377,7 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
         <v>6</v>
@@ -3395,7 +3395,7 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3454,7 +3454,7 @@
         <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
         <v>10</v>
@@ -3641,7 +3641,7 @@
         <v>95.2</v>
       </c>
       <c r="Q4">
-        <v>88.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R4">
         <v>93.8</v>
@@ -3700,7 +3700,7 @@
         <v>94</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R5">
         <v>93.8</v>
@@ -3759,7 +3759,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R6">
         <v>98.8</v>
@@ -4054,7 +4054,7 @@
         <v>95.2</v>
       </c>
       <c r="Q11">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4113,7 +4113,7 @@
         <v>94</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R12">
         <v>92.5</v>
@@ -4349,7 +4349,7 @@
         <v>95.2</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R16">
         <v>97.5</v>
@@ -4408,7 +4408,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q17">
-        <v>90.7</v>
+        <v>93.8</v>
       </c>
       <c r="R17">
         <v>95</v>
@@ -4880,7 +4880,7 @@
         <v>95.2</v>
       </c>
       <c r="Q25">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R25">
         <v>97.5</v>
@@ -4939,7 +4939,7 @@
         <v>95.2</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R26">
         <v>93.8</v>
@@ -4998,7 +4998,7 @@
         <v>94</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R27">
         <v>96.3</v>
@@ -5175,7 +5175,7 @@
         <v>94</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R30">
         <v>90</v>
@@ -5234,7 +5234,7 @@
         <v>95.2</v>
       </c>
       <c r="Q31">
-        <v>93</v>
+        <v>93.8</v>
       </c>
       <c r="R31">
         <v>88.8</v>
@@ -5293,7 +5293,7 @@
         <v>95.2</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R32">
         <v>98.8</v>
@@ -5352,7 +5352,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q33">
-        <v>90.7</v>
+        <v>92.2</v>
       </c>
       <c r="R33">
         <v>95</v>
@@ -5647,7 +5647,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q38">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R38">
         <v>86.3</v>
@@ -5706,7 +5706,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q39">
-        <v>90.7</v>
+        <v>92.2</v>
       </c>
       <c r="R39">
         <v>93.8</v>
@@ -5886,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
